--- a/immunizations/ValueSet-IMMZ.Z.DE8.xlsx
+++ b/immunizations/ValueSet-IMMZ.Z.DE8.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T12:12:05+00:00</t>
+    <t>2026-10-02T09:52:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
